--- a/output/yearly_population_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_26_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6222</v>
+        <v>5625</v>
       </c>
       <c r="C2" t="n">
-        <v>3879</v>
+        <v>9849</v>
       </c>
       <c r="D2" t="n">
-        <v>28939</v>
+        <v>26487</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3622</v>
+        <v>2951</v>
       </c>
       <c r="C3" t="n">
-        <v>5303</v>
+        <v>8568</v>
       </c>
       <c r="D3" t="n">
-        <v>15895</v>
+        <v>18296</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2984</v>
+        <v>2339</v>
       </c>
       <c r="C4" t="n">
-        <v>4859</v>
+        <v>5935</v>
       </c>
       <c r="D4" t="n">
-        <v>7245</v>
+        <v>8535</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1922</v>
+        <v>1554</v>
       </c>
       <c r="C5" t="n">
-        <v>4000</v>
+        <v>4330</v>
       </c>
       <c r="D5" t="n">
-        <v>2816</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1002</v>
+        <v>921</v>
       </c>
       <c r="C6" t="n">
-        <v>3181</v>
+        <v>3323</v>
       </c>
       <c r="D6" t="n">
-        <v>1210</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>2150</v>
+        <v>2441</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C8" t="n">
-        <v>1124</v>
+        <v>1278</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>455</v>
+        <v>501</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6143</v>
+        <v>5959</v>
       </c>
       <c r="C2" t="n">
-        <v>8296</v>
+        <v>14864</v>
       </c>
       <c r="D2" t="n">
-        <v>29713</v>
+        <v>31820</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3861</v>
+        <v>3308</v>
       </c>
       <c r="C3" t="n">
-        <v>4116</v>
+        <v>8059</v>
       </c>
       <c r="D3" t="n">
-        <v>16600</v>
+        <v>18144</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2790</v>
+        <v>2241</v>
       </c>
       <c r="C4" t="n">
-        <v>4920</v>
+        <v>7024</v>
       </c>
       <c r="D4" t="n">
-        <v>8436</v>
+        <v>9692</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2118</v>
+        <v>1661</v>
       </c>
       <c r="C5" t="n">
-        <v>4312</v>
+        <v>4907</v>
       </c>
       <c r="D5" t="n">
-        <v>3383</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1258</v>
+        <v>1075</v>
       </c>
       <c r="C6" t="n">
-        <v>3480</v>
+        <v>3726</v>
       </c>
       <c r="D6" t="n">
-        <v>1440</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>600</v>
+        <v>562</v>
       </c>
       <c r="C7" t="n">
-        <v>2603</v>
+        <v>2787</v>
       </c>
       <c r="D7" t="n">
-        <v>730</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C8" t="n">
-        <v>1544</v>
+        <v>1756</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>730</v>
+        <v>800</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6638</v>
+        <v>6179</v>
       </c>
       <c r="C2" t="n">
-        <v>8450</v>
+        <v>12351</v>
       </c>
       <c r="D2" t="n">
-        <v>27325</v>
+        <v>29222</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3890</v>
+        <v>3519</v>
       </c>
       <c r="C3" t="n">
-        <v>5159</v>
+        <v>9523</v>
       </c>
       <c r="D3" t="n">
-        <v>17111</v>
+        <v>18623</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2738</v>
+        <v>2255</v>
       </c>
       <c r="C4" t="n">
-        <v>4470</v>
+        <v>7237</v>
       </c>
       <c r="D4" t="n">
-        <v>9274</v>
+        <v>10614</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2127</v>
+        <v>1696</v>
       </c>
       <c r="C5" t="n">
-        <v>4431</v>
+        <v>5658</v>
       </c>
       <c r="D5" t="n">
-        <v>4007</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="6">
@@ -1458,10 +1458,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1452</v>
+        <v>1181</v>
       </c>
       <c r="C6" t="n">
-        <v>3750</v>
+        <v>4111</v>
       </c>
       <c r="D6" t="n">
         <v>1668</v>
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>766</v>
+        <v>676</v>
       </c>
       <c r="C7" t="n">
-        <v>2954</v>
+        <v>3117</v>
       </c>
       <c r="D7" t="n">
-        <v>819</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="C8" t="n">
-        <v>1933</v>
+        <v>2122</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>1025</v>
+        <v>1146</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1584,7 +1584,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>68</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6181</v>
+        <v>5788</v>
       </c>
       <c r="C2" t="n">
-        <v>5813</v>
+        <v>8695</v>
       </c>
       <c r="D2" t="n">
-        <v>22681</v>
+        <v>24271</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4785</v>
+        <v>4079</v>
       </c>
       <c r="C3" t="n">
-        <v>7744</v>
+        <v>13454</v>
       </c>
       <c r="D3" t="n">
-        <v>18454</v>
+        <v>20244</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1965</v>
+        <v>1567</v>
       </c>
       <c r="C4" t="n">
-        <v>6699</v>
+        <v>9252</v>
       </c>
       <c r="D4" t="n">
-        <v>8823</v>
+        <v>9959</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1341</v>
+        <v>1091</v>
       </c>
       <c r="C5" t="n">
-        <v>3675</v>
+        <v>4028</v>
       </c>
       <c r="D5" t="n">
-        <v>2711</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>707</v>
+        <v>624</v>
       </c>
       <c r="C6" t="n">
-        <v>2894</v>
+        <v>3054</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>1894</v>
+        <v>2079</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>1004</v>
+        <v>1123</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1881,7 +1881,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>66</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3916</v>
+        <v>3630</v>
       </c>
       <c r="C2" t="n">
-        <v>2891</v>
+        <v>5142</v>
       </c>
       <c r="D2" t="n">
-        <v>16303</v>
+        <v>17143</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4668</v>
+        <v>4122</v>
       </c>
       <c r="C3" t="n">
-        <v>6237</v>
+        <v>10382</v>
       </c>
       <c r="D3" t="n">
-        <v>18143</v>
+        <v>19625</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2641</v>
+        <v>2140</v>
       </c>
       <c r="C4" t="n">
-        <v>7298</v>
+        <v>11181</v>
       </c>
       <c r="D4" t="n">
-        <v>10026</v>
+        <v>11328</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1496</v>
+        <v>1194</v>
       </c>
       <c r="C5" t="n">
-        <v>4958</v>
+        <v>6193</v>
       </c>
       <c r="D5" t="n">
-        <v>3443</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>849</v>
+        <v>732</v>
       </c>
       <c r="C6" t="n">
-        <v>3340</v>
+        <v>3559</v>
       </c>
       <c r="D6" t="n">
-        <v>999</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>2306</v>
+        <v>2480</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>1305</v>
+        <v>1437</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>164</v>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5710</v>
+        <v>2909</v>
       </c>
       <c r="C2" t="n">
-        <v>6454</v>
+        <v>4596</v>
       </c>
       <c r="D2" t="n">
-        <v>15684</v>
+        <v>21119</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3693</v>
+        <v>3332</v>
       </c>
       <c r="C3" t="n">
-        <v>4136</v>
+        <v>7098</v>
       </c>
       <c r="D3" t="n">
-        <v>16673</v>
+        <v>18157</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3003</v>
+        <v>2518</v>
       </c>
       <c r="C4" t="n">
-        <v>6626</v>
+        <v>10572</v>
       </c>
       <c r="D4" t="n">
-        <v>11045</v>
+        <v>12149</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1762</v>
+        <v>1402</v>
       </c>
       <c r="C5" t="n">
-        <v>5955</v>
+        <v>8374</v>
       </c>
       <c r="D5" t="n">
-        <v>4349</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1031</v>
+        <v>841</v>
       </c>
       <c r="C6" t="n">
-        <v>4070</v>
+        <v>4638</v>
       </c>
       <c r="D6" t="n">
-        <v>1337</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>2773</v>
+        <v>2947</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>1719</v>
+        <v>1849</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>803</v>
+        <v>837</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3357</v>
+        <v>1764</v>
       </c>
       <c r="C2" t="n">
-        <v>3021</v>
+        <v>2282</v>
       </c>
       <c r="D2" t="n">
-        <v>10971</v>
+        <v>14890</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4030</v>
+        <v>3154</v>
       </c>
       <c r="C3" t="n">
-        <v>4789</v>
+        <v>6067</v>
       </c>
       <c r="D3" t="n">
-        <v>16196</v>
+        <v>18063</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3324</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>6311</v>
+        <v>10401</v>
       </c>
       <c r="D4" t="n">
-        <v>11767</v>
+        <v>12913</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1835</v>
+        <v>1461</v>
       </c>
       <c r="C5" t="n">
-        <v>6972</v>
+        <v>10089</v>
       </c>
       <c r="D5" t="n">
-        <v>4595</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>687</v>
       </c>
       <c r="C6" t="n">
-        <v>5001</v>
+        <v>5433</v>
       </c>
       <c r="D6" t="n">
-        <v>1308</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>3010</v>
+        <v>3163</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>1309</v>
+        <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>163</v>
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3260</v>
+        <v>1864</v>
       </c>
       <c r="C2" t="n">
-        <v>5735</v>
+        <v>2925</v>
       </c>
       <c r="D2" t="n">
-        <v>10051</v>
+        <v>16012</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3161</v>
+        <v>2243</v>
       </c>
       <c r="C3" t="n">
-        <v>3531</v>
+        <v>3963</v>
       </c>
       <c r="D3" t="n">
-        <v>14397</v>
+        <v>16471</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3185</v>
+        <v>2536</v>
       </c>
       <c r="C4" t="n">
-        <v>5509</v>
+        <v>8329</v>
       </c>
       <c r="D4" t="n">
-        <v>12132</v>
+        <v>13311</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2172</v>
+        <v>1739</v>
       </c>
       <c r="C5" t="n">
-        <v>6595</v>
+        <v>10107</v>
       </c>
       <c r="D5" t="n">
-        <v>5601</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1099</v>
+        <v>881</v>
       </c>
       <c r="C6" t="n">
-        <v>5836</v>
+        <v>7272</v>
       </c>
       <c r="D6" t="n">
-        <v>1732</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>3867</v>
+        <v>4038</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1950</v>
+        <v>1994</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>43</v>
+      </c>
+      <c r="D14" t="n">
         <v>45</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2272</v>
+        <v>1299</v>
       </c>
       <c r="C2" t="n">
-        <v>3271</v>
+        <v>1760</v>
       </c>
       <c r="D2" t="n">
-        <v>8220</v>
+        <v>11597</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2797</v>
+        <v>1868</v>
       </c>
       <c r="C3" t="n">
-        <v>3996</v>
+        <v>3265</v>
       </c>
       <c r="D3" t="n">
-        <v>13092</v>
+        <v>15549</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2924</v>
+        <v>2263</v>
       </c>
       <c r="C4" t="n">
-        <v>4736</v>
+        <v>6719</v>
       </c>
       <c r="D4" t="n">
-        <v>12184</v>
+        <v>13428</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2370</v>
+        <v>1862</v>
       </c>
       <c r="C5" t="n">
-        <v>6314</v>
+        <v>9687</v>
       </c>
       <c r="D5" t="n">
-        <v>6290</v>
+        <v>6553</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1288</v>
+        <v>1013</v>
       </c>
       <c r="C6" t="n">
-        <v>6315</v>
+        <v>8372</v>
       </c>
       <c r="D6" t="n">
-        <v>2079</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="C7" t="n">
-        <v>4613</v>
+        <v>4971</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2447</v>
+        <v>2493</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>754</v>
+        <v>696</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4067</v>
+        <v>1843</v>
       </c>
       <c r="C2" t="n">
-        <v>6987</v>
+        <v>10466</v>
       </c>
       <c r="D2" t="n">
-        <v>15680</v>
+        <v>14304</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2197</v>
+        <v>1414</v>
       </c>
       <c r="C3" t="n">
-        <v>3287</v>
+        <v>2409</v>
       </c>
       <c r="D3" t="n">
-        <v>11669</v>
+        <v>14136</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2502</v>
+        <v>1852</v>
       </c>
       <c r="C4" t="n">
-        <v>4317</v>
+        <v>5186</v>
       </c>
       <c r="D4" t="n">
-        <v>11944</v>
+        <v>13304</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2336</v>
+        <v>1838</v>
       </c>
       <c r="C5" t="n">
-        <v>5531</v>
+        <v>8345</v>
       </c>
       <c r="D5" t="n">
-        <v>6830</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1545</v>
+        <v>1191</v>
       </c>
       <c r="C6" t="n">
-        <v>6260</v>
+        <v>8784</v>
       </c>
       <c r="D6" t="n">
-        <v>2617</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>538</v>
+        <v>402</v>
       </c>
       <c r="C7" t="n">
-        <v>5306</v>
+        <v>6168</v>
       </c>
       <c r="D7" t="n">
-        <v>925</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>3210</v>
+        <v>3342</v>
       </c>
       <c r="D8" t="n">
-        <v>447</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1325</v>
+        <v>1248</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>86</v>
+      </c>
+      <c r="D12" t="n">
         <v>92</v>
-      </c>
-      <c r="D12" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5253</v>
+        <v>5216</v>
       </c>
       <c r="C2" t="n">
-        <v>11677</v>
+        <v>15037</v>
       </c>
       <c r="D2" t="n">
-        <v>18957</v>
+        <v>12238</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2908</v>
+        <v>1347</v>
       </c>
       <c r="C2" t="n">
-        <v>3969</v>
+        <v>6195</v>
       </c>
       <c r="D2" t="n">
-        <v>11541</v>
+        <v>10642</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3018</v>
+        <v>1968</v>
       </c>
       <c r="C3" t="n">
-        <v>4429</v>
+        <v>4354</v>
       </c>
       <c r="D3" t="n">
-        <v>13008</v>
+        <v>15393</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3436</v>
+        <v>2628</v>
       </c>
       <c r="C4" t="n">
-        <v>6190</v>
+        <v>7917</v>
       </c>
       <c r="D4" t="n">
-        <v>12237</v>
+        <v>13465</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1492</v>
+        <v>1117</v>
       </c>
       <c r="C5" t="n">
-        <v>8457</v>
+        <v>12266</v>
       </c>
       <c r="D5" t="n">
-        <v>6265</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>497</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>6488</v>
+        <v>7594</v>
       </c>
       <c r="D6" t="n">
-        <v>2070</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>3145</v>
+        <v>3275</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1298</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="n">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>84</v>
+      </c>
+      <c r="D11" t="n">
         <v>90</v>
-      </c>
-      <c r="D11" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6186</v>
+        <v>6651</v>
       </c>
       <c r="C2" t="n">
-        <v>6192</v>
+        <v>6686</v>
       </c>
       <c r="D2" t="n">
-        <v>15633</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2232</v>
+        <v>2217</v>
       </c>
       <c r="C3" t="n">
-        <v>5885</v>
+        <v>7578</v>
       </c>
       <c r="D3" t="n">
-        <v>3824</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="4">
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4616,7 +4616,7 @@
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4654</v>
+        <v>4415</v>
       </c>
       <c r="C2" t="n">
-        <v>6289</v>
+        <v>5400</v>
       </c>
       <c r="D2" t="n">
-        <v>16397</v>
+        <v>18861</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3455</v>
+        <v>3639</v>
       </c>
       <c r="C3" t="n">
-        <v>5225</v>
+        <v>6099</v>
       </c>
       <c r="D3" t="n">
-        <v>5526</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="C4" t="n">
-        <v>3492</v>
+        <v>4483</v>
       </c>
       <c r="D4" t="n">
-        <v>1952</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4910,7 +4910,7 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5273</v>
+        <v>4729</v>
       </c>
       <c r="C2" t="n">
-        <v>4991</v>
+        <v>6340</v>
       </c>
       <c r="D2" t="n">
-        <v>17586</v>
+        <v>33381</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3325</v>
+        <v>3342</v>
       </c>
       <c r="C3" t="n">
-        <v>5024</v>
+        <v>4964</v>
       </c>
       <c r="D3" t="n">
-        <v>6867</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1895</v>
+        <v>1938</v>
       </c>
       <c r="C4" t="n">
-        <v>4350</v>
+        <v>5289</v>
       </c>
       <c r="D4" t="n">
-        <v>2578</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C5" t="n">
-        <v>2008</v>
+        <v>2507</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7074</v>
+        <v>4849</v>
       </c>
       <c r="C2" t="n">
-        <v>7948</v>
+        <v>5250</v>
       </c>
       <c r="D2" t="n">
-        <v>25789</v>
+        <v>32594</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3470</v>
+        <v>3277</v>
       </c>
       <c r="C3" t="n">
-        <v>4406</v>
+        <v>4934</v>
       </c>
       <c r="D3" t="n">
-        <v>8012</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2191</v>
+        <v>2234</v>
       </c>
       <c r="C4" t="n">
-        <v>4573</v>
+        <v>5007</v>
       </c>
       <c r="D4" t="n">
-        <v>3281</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C5" t="n">
-        <v>3180</v>
+        <v>3846</v>
       </c>
       <c r="D5" t="n">
-        <v>1458</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="6">
@@ -5504,10 +5504,10 @@
         <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>1149</v>
+        <v>1400</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7444</v>
+        <v>5333</v>
       </c>
       <c r="C2" t="n">
-        <v>5272</v>
+        <v>9267</v>
       </c>
       <c r="D2" t="n">
-        <v>31759</v>
+        <v>40522</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3804</v>
+        <v>2923</v>
       </c>
       <c r="C3" t="n">
-        <v>5066</v>
+        <v>4216</v>
       </c>
       <c r="D3" t="n">
-        <v>9548</v>
+        <v>11819</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1732</v>
+        <v>1689</v>
       </c>
       <c r="C4" t="n">
-        <v>3632</v>
+        <v>4021</v>
       </c>
       <c r="D4" t="n">
-        <v>3526</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="C5" t="n">
-        <v>2846</v>
+        <v>3231</v>
       </c>
       <c r="D5" t="n">
-        <v>1388</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>1442</v>
+        <v>1731</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>475</v>
+        <v>545</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5262</v>
+        <v>4456</v>
       </c>
       <c r="C2" t="n">
-        <v>8223</v>
+        <v>9967</v>
       </c>
       <c r="D2" t="n">
-        <v>31165</v>
+        <v>37821</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4652</v>
+        <v>3396</v>
       </c>
       <c r="C3" t="n">
-        <v>4456</v>
+        <v>6134</v>
       </c>
       <c r="D3" t="n">
-        <v>12576</v>
+        <v>15771</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2423</v>
+        <v>1989</v>
       </c>
       <c r="C4" t="n">
-        <v>4423</v>
+        <v>4053</v>
       </c>
       <c r="D4" t="n">
-        <v>4598</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="C5" t="n">
-        <v>3247</v>
+        <v>3618</v>
       </c>
       <c r="D5" t="n">
-        <v>1776</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C6" t="n">
-        <v>2219</v>
+        <v>2545</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>1014</v>
+        <v>1195</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4653</v>
+        <v>3989</v>
       </c>
       <c r="C2" t="n">
-        <v>6536</v>
+        <v>12759</v>
       </c>
       <c r="D2" t="n">
-        <v>30335</v>
+        <v>28590</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4081</v>
+        <v>3244</v>
       </c>
       <c r="C3" t="n">
-        <v>5612</v>
+        <v>7077</v>
       </c>
       <c r="D3" t="n">
-        <v>14644</v>
+        <v>18012</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2996</v>
+        <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>4349</v>
+        <v>5107</v>
       </c>
       <c r="D4" t="n">
-        <v>5989</v>
+        <v>6806</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1540</v>
+        <v>1358</v>
       </c>
       <c r="C5" t="n">
-        <v>3811</v>
+        <v>3737</v>
       </c>
       <c r="D5" t="n">
-        <v>2236</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="C6" t="n">
-        <v>2705</v>
+        <v>3072</v>
       </c>
       <c r="D6" t="n">
-        <v>1027</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>1639</v>
+        <v>1882</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>686</v>
+        <v>784</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_26_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5625</v>
+        <v>6821</v>
       </c>
       <c r="C2" t="n">
-        <v>9849</v>
+        <v>6465</v>
       </c>
       <c r="D2" t="n">
-        <v>26487</v>
+        <v>21579</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2951</v>
+        <v>3384</v>
       </c>
       <c r="C3" t="n">
-        <v>8568</v>
+        <v>7209</v>
       </c>
       <c r="D3" t="n">
-        <v>18296</v>
+        <v>11650</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2339</v>
+        <v>2805</v>
       </c>
       <c r="C4" t="n">
-        <v>5935</v>
+        <v>7152</v>
       </c>
       <c r="D4" t="n">
-        <v>8535</v>
+        <v>6712</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1554</v>
+        <v>1858</v>
       </c>
       <c r="C5" t="n">
-        <v>4330</v>
+        <v>6396</v>
       </c>
       <c r="D5" t="n">
-        <v>2882</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>921</v>
+        <v>1120</v>
       </c>
       <c r="C6" t="n">
-        <v>3323</v>
+        <v>4166</v>
       </c>
       <c r="D6" t="n">
-        <v>1159</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>549</v>
       </c>
       <c r="C7" t="n">
-        <v>2441</v>
+        <v>2262</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="C8" t="n">
-        <v>1278</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="n">
         <v>428</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5959</v>
+        <v>7372</v>
       </c>
       <c r="C2" t="n">
-        <v>14864</v>
+        <v>6341</v>
       </c>
       <c r="D2" t="n">
-        <v>31820</v>
+        <v>26252</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3308</v>
+        <v>3886</v>
       </c>
       <c r="C3" t="n">
-        <v>8059</v>
+        <v>6098</v>
       </c>
       <c r="D3" t="n">
-        <v>18144</v>
+        <v>12156</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2241</v>
+        <v>2606</v>
       </c>
       <c r="C4" t="n">
-        <v>7024</v>
+        <v>6960</v>
       </c>
       <c r="D4" t="n">
-        <v>9692</v>
+        <v>7201</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1661</v>
+        <v>1989</v>
       </c>
       <c r="C5" t="n">
-        <v>4907</v>
+        <v>6596</v>
       </c>
       <c r="D5" t="n">
-        <v>3662</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1075</v>
+        <v>1297</v>
       </c>
       <c r="C6" t="n">
-        <v>3726</v>
+        <v>5028</v>
       </c>
       <c r="D6" t="n">
-        <v>1380</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>562</v>
+        <v>707</v>
       </c>
       <c r="C7" t="n">
-        <v>2787</v>
+        <v>3041</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>237</v>
+        <v>300</v>
       </c>
       <c r="C8" t="n">
-        <v>1756</v>
+        <v>1559</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>800</v>
+        <v>675</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6179</v>
+        <v>9840</v>
       </c>
       <c r="C2" t="n">
-        <v>12351</v>
+        <v>8027</v>
       </c>
       <c r="D2" t="n">
-        <v>29222</v>
+        <v>25422</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3519</v>
+        <v>4242</v>
       </c>
       <c r="C3" t="n">
-        <v>9523</v>
+        <v>5518</v>
       </c>
       <c r="D3" t="n">
-        <v>18623</v>
+        <v>13069</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2255</v>
+        <v>2657</v>
       </c>
       <c r="C4" t="n">
-        <v>7237</v>
+        <v>6459</v>
       </c>
       <c r="D4" t="n">
-        <v>10614</v>
+        <v>7695</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1696</v>
+        <v>1986</v>
       </c>
       <c r="C5" t="n">
-        <v>5658</v>
+        <v>6538</v>
       </c>
       <c r="D5" t="n">
-        <v>4325</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1181</v>
+        <v>1421</v>
       </c>
       <c r="C6" t="n">
-        <v>4111</v>
+        <v>5538</v>
       </c>
       <c r="D6" t="n">
-        <v>1668</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>676</v>
+        <v>834</v>
       </c>
       <c r="C7" t="n">
-        <v>3117</v>
+        <v>3769</v>
       </c>
       <c r="D7" t="n">
-        <v>787</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>314</v>
+        <v>396</v>
       </c>
       <c r="C8" t="n">
-        <v>2122</v>
+        <v>2110</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="C9" t="n">
-        <v>1146</v>
+        <v>979</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>488</v>
+        <v>426</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1618,7 +1618,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5788</v>
+        <v>8891</v>
       </c>
       <c r="C2" t="n">
-        <v>8695</v>
+        <v>5651</v>
       </c>
       <c r="D2" t="n">
-        <v>24271</v>
+        <v>20964</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4079</v>
+        <v>4865</v>
       </c>
       <c r="C3" t="n">
-        <v>13454</v>
+        <v>8858</v>
       </c>
       <c r="D3" t="n">
-        <v>20244</v>
+        <v>14356</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1567</v>
+        <v>1835</v>
       </c>
       <c r="C4" t="n">
-        <v>9252</v>
+        <v>9686</v>
       </c>
       <c r="D4" t="n">
-        <v>9959</v>
+        <v>7427</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1091</v>
+        <v>1313</v>
       </c>
       <c r="C5" t="n">
-        <v>4028</v>
+        <v>5427</v>
       </c>
       <c r="D5" t="n">
-        <v>2755</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>624</v>
+        <v>770</v>
       </c>
       <c r="C6" t="n">
-        <v>3054</v>
+        <v>3693</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>2079</v>
+        <v>2067</v>
       </c>
       <c r="D7" t="n">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>1123</v>
+        <v>959</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
         <v>199</v>
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>157</v>
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1915,7 +1915,7 @@
         <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3630</v>
+        <v>5245</v>
       </c>
       <c r="C2" t="n">
-        <v>5142</v>
+        <v>2779</v>
       </c>
       <c r="D2" t="n">
-        <v>17143</v>
+        <v>14810</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4122</v>
+        <v>5551</v>
       </c>
       <c r="C3" t="n">
-        <v>10382</v>
+        <v>6767</v>
       </c>
       <c r="D3" t="n">
-        <v>19625</v>
+        <v>14565</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2140</v>
+        <v>2556</v>
       </c>
       <c r="C4" t="n">
-        <v>11181</v>
+        <v>9482</v>
       </c>
       <c r="D4" t="n">
-        <v>11328</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1194</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>6193</v>
+        <v>7250</v>
       </c>
       <c r="D5" t="n">
-        <v>3554</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>732</v>
+        <v>900</v>
       </c>
       <c r="C6" t="n">
-        <v>3559</v>
+        <v>4449</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>2480</v>
+        <v>2662</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>1437</v>
+        <v>1261</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
         <v>205</v>
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2212,7 +2212,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2909</v>
+        <v>4991</v>
       </c>
       <c r="C2" t="n">
-        <v>4596</v>
+        <v>6872</v>
       </c>
       <c r="D2" t="n">
-        <v>21119</v>
+        <v>13755</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3332</v>
+        <v>4558</v>
       </c>
       <c r="C3" t="n">
-        <v>7098</v>
+        <v>4424</v>
       </c>
       <c r="D3" t="n">
-        <v>18157</v>
+        <v>13619</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2518</v>
+        <v>3263</v>
       </c>
       <c r="C4" t="n">
-        <v>10572</v>
+        <v>8007</v>
       </c>
       <c r="D4" t="n">
-        <v>12149</v>
+        <v>9103</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1402</v>
+        <v>1685</v>
       </c>
       <c r="C5" t="n">
-        <v>8374</v>
+        <v>8106</v>
       </c>
       <c r="D5" t="n">
-        <v>4640</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>841</v>
+        <v>1026</v>
       </c>
       <c r="C6" t="n">
-        <v>4638</v>
+        <v>5660</v>
       </c>
       <c r="D6" t="n">
-        <v>1316</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>486</v>
       </c>
       <c r="C7" t="n">
-        <v>2947</v>
+        <v>3396</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="C8" t="n">
-        <v>1849</v>
+        <v>1822</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>837</v>
+        <v>750</v>
       </c>
       <c r="D9" t="n">
         <v>261</v>
@@ -2450,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>22</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1764</v>
+        <v>3031</v>
       </c>
       <c r="C2" t="n">
-        <v>2282</v>
+        <v>3318</v>
       </c>
       <c r="D2" t="n">
-        <v>14890</v>
+        <v>9595</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3154</v>
+        <v>4495</v>
       </c>
       <c r="C3" t="n">
-        <v>6067</v>
+        <v>5087</v>
       </c>
       <c r="D3" t="n">
-        <v>18063</v>
+        <v>13328</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>3588</v>
       </c>
       <c r="C4" t="n">
-        <v>10401</v>
+        <v>7508</v>
       </c>
       <c r="D4" t="n">
-        <v>12913</v>
+        <v>9688</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1461</v>
+        <v>1754</v>
       </c>
       <c r="C5" t="n">
-        <v>10089</v>
+        <v>9396</v>
       </c>
       <c r="D5" t="n">
-        <v>4753</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>687</v>
+        <v>856</v>
       </c>
       <c r="C6" t="n">
-        <v>5433</v>
+        <v>6601</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>3163</v>
+        <v>3446</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1345</v>
+        <v>1270</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2820,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>21</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1864</v>
+        <v>3713</v>
       </c>
       <c r="C2" t="n">
-        <v>2925</v>
+        <v>5267</v>
       </c>
       <c r="D2" t="n">
-        <v>16012</v>
+        <v>8641</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2243</v>
+        <v>3344</v>
       </c>
       <c r="C3" t="n">
-        <v>3963</v>
+        <v>3840</v>
       </c>
       <c r="D3" t="n">
-        <v>16471</v>
+        <v>11975</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2536</v>
+        <v>3442</v>
       </c>
       <c r="C4" t="n">
-        <v>8329</v>
+        <v>6308</v>
       </c>
       <c r="D4" t="n">
-        <v>13311</v>
+        <v>9952</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1739</v>
+        <v>2188</v>
       </c>
       <c r="C5" t="n">
-        <v>10107</v>
+        <v>8384</v>
       </c>
       <c r="D5" t="n">
-        <v>5829</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>1087</v>
       </c>
       <c r="C6" t="n">
-        <v>7272</v>
+        <v>7824</v>
       </c>
       <c r="D6" t="n">
-        <v>1691</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>4038</v>
+        <v>4684</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1994</v>
+        <v>2062</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>612</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3131,7 +3131,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1299</v>
+        <v>2561</v>
       </c>
       <c r="C2" t="n">
-        <v>1760</v>
+        <v>3354</v>
       </c>
       <c r="D2" t="n">
-        <v>11597</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1868</v>
+        <v>3032</v>
       </c>
       <c r="C3" t="n">
-        <v>3265</v>
+        <v>3986</v>
       </c>
       <c r="D3" t="n">
-        <v>15549</v>
+        <v>10969</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2263</v>
+        <v>3142</v>
       </c>
       <c r="C4" t="n">
-        <v>6719</v>
+        <v>5387</v>
       </c>
       <c r="D4" t="n">
-        <v>13428</v>
+        <v>9997</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1862</v>
+        <v>2394</v>
       </c>
       <c r="C5" t="n">
-        <v>9687</v>
+        <v>7733</v>
       </c>
       <c r="D5" t="n">
-        <v>6553</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1013</v>
+        <v>1273</v>
       </c>
       <c r="C6" t="n">
-        <v>8372</v>
+        <v>8322</v>
       </c>
       <c r="D6" t="n">
-        <v>2021</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>4971</v>
+        <v>5741</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2493</v>
+        <v>2664</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1843</v>
+        <v>3320</v>
       </c>
       <c r="C2" t="n">
-        <v>10466</v>
+        <v>11400</v>
       </c>
       <c r="D2" t="n">
-        <v>14304</v>
+        <v>12653</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1414</v>
+        <v>2416</v>
       </c>
       <c r="C3" t="n">
-        <v>2409</v>
+        <v>3334</v>
       </c>
       <c r="D3" t="n">
-        <v>14136</v>
+        <v>9829</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1852</v>
+        <v>2697</v>
       </c>
       <c r="C4" t="n">
-        <v>5186</v>
+        <v>4696</v>
       </c>
       <c r="D4" t="n">
-        <v>13304</v>
+        <v>9727</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1838</v>
+        <v>2431</v>
       </c>
       <c r="C5" t="n">
-        <v>8345</v>
+        <v>6648</v>
       </c>
       <c r="D5" t="n">
-        <v>7148</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1191</v>
+        <v>1522</v>
       </c>
       <c r="C6" t="n">
-        <v>8784</v>
+        <v>8033</v>
       </c>
       <c r="D6" t="n">
-        <v>2560</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>517</v>
       </c>
       <c r="C7" t="n">
-        <v>6168</v>
+        <v>6674</v>
       </c>
       <c r="D7" t="n">
-        <v>873</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>3342</v>
+        <v>3744</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1248</v>
+        <v>1317</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" t="n">
         <v>36</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5216</v>
+        <v>7797</v>
       </c>
       <c r="C2" t="n">
-        <v>15037</v>
+        <v>11101</v>
       </c>
       <c r="D2" t="n">
-        <v>12238</v>
+        <v>9623</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1347</v>
+        <v>2402</v>
       </c>
       <c r="C2" t="n">
-        <v>6195</v>
+        <v>6657</v>
       </c>
       <c r="D2" t="n">
-        <v>10642</v>
+        <v>9413</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1968</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>4354</v>
+        <v>5374</v>
       </c>
       <c r="D3" t="n">
-        <v>15393</v>
+        <v>10798</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2628</v>
+        <v>3603</v>
       </c>
       <c r="C4" t="n">
-        <v>7917</v>
+        <v>6966</v>
       </c>
       <c r="D4" t="n">
-        <v>13465</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1117</v>
+        <v>1451</v>
       </c>
       <c r="C5" t="n">
-        <v>12266</v>
+        <v>10588</v>
       </c>
       <c r="D5" t="n">
-        <v>6426</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>371</v>
+        <v>477</v>
       </c>
       <c r="C6" t="n">
-        <v>7594</v>
+        <v>8036</v>
       </c>
       <c r="D6" t="n">
-        <v>1982</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>3275</v>
+        <v>3669</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1223</v>
+        <v>1290</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" t="n">
         <v>35</v>
-      </c>
-      <c r="D13" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6651</v>
+        <v>8181</v>
       </c>
       <c r="C2" t="n">
-        <v>6686</v>
+        <v>6299</v>
       </c>
       <c r="D2" t="n">
-        <v>13724</v>
+        <v>8871</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2217</v>
+        <v>3311</v>
       </c>
       <c r="C3" t="n">
-        <v>7578</v>
+        <v>5594</v>
       </c>
       <c r="D3" t="n">
-        <v>2695</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4415</v>
+        <v>5239</v>
       </c>
       <c r="C2" t="n">
-        <v>5400</v>
+        <v>7190</v>
       </c>
       <c r="D2" t="n">
-        <v>18861</v>
+        <v>18074</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3639</v>
+        <v>4720</v>
       </c>
       <c r="C3" t="n">
-        <v>6099</v>
+        <v>5168</v>
       </c>
       <c r="D3" t="n">
-        <v>4349</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>997</v>
+        <v>1473</v>
       </c>
       <c r="C4" t="n">
-        <v>4483</v>
+        <v>3321</v>
       </c>
       <c r="D4" t="n">
-        <v>1724</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>406</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4729</v>
+        <v>4570</v>
       </c>
       <c r="C2" t="n">
-        <v>6340</v>
+        <v>10801</v>
       </c>
       <c r="D2" t="n">
-        <v>33381</v>
+        <v>30847</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3342</v>
+        <v>4104</v>
       </c>
       <c r="C3" t="n">
-        <v>4964</v>
+        <v>5419</v>
       </c>
       <c r="D3" t="n">
-        <v>6357</v>
+        <v>5349</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1938</v>
+        <v>2635</v>
       </c>
       <c r="C4" t="n">
-        <v>5289</v>
+        <v>4248</v>
       </c>
       <c r="D4" t="n">
-        <v>2175</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>462</v>
+        <v>652</v>
       </c>
       <c r="C5" t="n">
-        <v>2507</v>
+        <v>1912</v>
       </c>
       <c r="D5" t="n">
-        <v>1246</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
         <v>305</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>371</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4849</v>
+        <v>5701</v>
       </c>
       <c r="C2" t="n">
-        <v>5250</v>
+        <v>13727</v>
       </c>
       <c r="D2" t="n">
-        <v>32594</v>
+        <v>31016</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3277</v>
+        <v>3569</v>
       </c>
       <c r="C3" t="n">
-        <v>4934</v>
+        <v>7093</v>
       </c>
       <c r="D3" t="n">
-        <v>10017</v>
+        <v>8848</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2234</v>
+        <v>2865</v>
       </c>
       <c r="C4" t="n">
-        <v>5007</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="n">
-        <v>2871</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>969</v>
+        <v>1331</v>
       </c>
       <c r="C5" t="n">
-        <v>3846</v>
+        <v>3042</v>
       </c>
       <c r="D5" t="n">
-        <v>1368</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="C6" t="n">
-        <v>1400</v>
+        <v>1103</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
         <v>666</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>471</v>
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5591,7 +5591,7 @@
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5333</v>
+        <v>6861</v>
       </c>
       <c r="C2" t="n">
-        <v>9267</v>
+        <v>11261</v>
       </c>
       <c r="D2" t="n">
-        <v>40522</v>
+        <v>23640</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2923</v>
+        <v>3325</v>
       </c>
       <c r="C3" t="n">
-        <v>4216</v>
+        <v>8539</v>
       </c>
       <c r="D3" t="n">
-        <v>11819</v>
+        <v>10907</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1689</v>
+        <v>1978</v>
       </c>
       <c r="C4" t="n">
-        <v>4021</v>
+        <v>4934</v>
       </c>
       <c r="D4" t="n">
-        <v>3479</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>831</v>
+        <v>1094</v>
       </c>
       <c r="C5" t="n">
-        <v>3231</v>
+        <v>2841</v>
       </c>
       <c r="D5" t="n">
-        <v>1284</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>1731</v>
+        <v>1388</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>545</v>
+        <v>454</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5840,7 +5840,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>221</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5868,7 +5868,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>148</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4456</v>
+        <v>5409</v>
       </c>
       <c r="C2" t="n">
-        <v>9967</v>
+        <v>7154</v>
       </c>
       <c r="D2" t="n">
-        <v>37821</v>
+        <v>17222</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3396</v>
+        <v>4242</v>
       </c>
       <c r="C3" t="n">
-        <v>6134</v>
+        <v>8700</v>
       </c>
       <c r="D3" t="n">
-        <v>15771</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1989</v>
+        <v>2287</v>
       </c>
       <c r="C4" t="n">
-        <v>4053</v>
+        <v>6977</v>
       </c>
       <c r="D4" t="n">
-        <v>5054</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1118</v>
+        <v>1368</v>
       </c>
       <c r="C5" t="n">
-        <v>3618</v>
+        <v>3987</v>
       </c>
       <c r="D5" t="n">
-        <v>1654</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>508</v>
+        <v>673</v>
       </c>
       <c r="C6" t="n">
-        <v>2545</v>
+        <v>2180</v>
       </c>
       <c r="D6" t="n">
-        <v>850</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>1195</v>
+        <v>966</v>
       </c>
       <c r="D7" t="n">
         <v>560</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
         <v>374</v>
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>172</v>
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>130</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6227,7 +6227,7 @@
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3989</v>
+        <v>4263</v>
       </c>
       <c r="C2" t="n">
-        <v>12759</v>
+        <v>9740</v>
       </c>
       <c r="D2" t="n">
-        <v>28590</v>
+        <v>14557</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3244</v>
+        <v>3949</v>
       </c>
       <c r="C3" t="n">
-        <v>7077</v>
+        <v>6853</v>
       </c>
       <c r="D3" t="n">
-        <v>18012</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2274</v>
+        <v>2750</v>
       </c>
       <c r="C4" t="n">
-        <v>5107</v>
+        <v>7774</v>
       </c>
       <c r="D4" t="n">
-        <v>6806</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1358</v>
+        <v>1604</v>
       </c>
       <c r="C5" t="n">
-        <v>3737</v>
+        <v>5444</v>
       </c>
       <c r="D5" t="n">
-        <v>2223</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>722</v>
+        <v>910</v>
       </c>
       <c r="C6" t="n">
-        <v>3072</v>
+        <v>3092</v>
       </c>
       <c r="D6" t="n">
-        <v>968</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>386</v>
       </c>
       <c r="C7" t="n">
-        <v>1882</v>
+        <v>1584</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>784</v>
+        <v>647</v>
       </c>
       <c r="D8" t="n">
         <v>401</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -6490,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>188</v>
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>148</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>

--- a/output/yearly_population_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_26_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6821</v>
+        <v>1097</v>
       </c>
       <c r="C2" t="n">
-        <v>6465</v>
+        <v>2596</v>
       </c>
       <c r="D2" t="n">
-        <v>21579</v>
+        <v>12927</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3384</v>
+        <v>1637</v>
       </c>
       <c r="C3" t="n">
-        <v>7209</v>
+        <v>6607</v>
       </c>
       <c r="D3" t="n">
-        <v>11650</v>
+        <v>15243</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2805</v>
+        <v>958</v>
       </c>
       <c r="C4" t="n">
-        <v>7152</v>
+        <v>7777</v>
       </c>
       <c r="D4" t="n">
-        <v>6712</v>
+        <v>7129</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1858</v>
+        <v>433</v>
       </c>
       <c r="C5" t="n">
-        <v>6396</v>
+        <v>5081</v>
       </c>
       <c r="D5" t="n">
-        <v>2550</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1120</v>
+        <v>207</v>
       </c>
       <c r="C6" t="n">
-        <v>4166</v>
+        <v>2313</v>
       </c>
       <c r="D6" t="n">
-        <v>1088</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>549</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>2262</v>
+        <v>855</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1069</v>
+        <v>360</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7372</v>
+        <v>744</v>
       </c>
       <c r="C2" t="n">
-        <v>6341</v>
+        <v>6960</v>
       </c>
       <c r="D2" t="n">
-        <v>26252</v>
+        <v>16471</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3886</v>
+        <v>1165</v>
       </c>
       <c r="C3" t="n">
-        <v>6098</v>
+        <v>3974</v>
       </c>
       <c r="D3" t="n">
-        <v>12156</v>
+        <v>13817</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2606</v>
+        <v>1106</v>
       </c>
       <c r="C4" t="n">
-        <v>6960</v>
+        <v>6986</v>
       </c>
       <c r="D4" t="n">
-        <v>7201</v>
+        <v>8392</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1989</v>
+        <v>591</v>
       </c>
       <c r="C5" t="n">
-        <v>6596</v>
+        <v>6421</v>
       </c>
       <c r="D5" t="n">
-        <v>3111</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1297</v>
+        <v>282</v>
       </c>
       <c r="C6" t="n">
-        <v>5028</v>
+        <v>3666</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>707</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>3041</v>
+        <v>1548</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1559</v>
+        <v>581</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9840</v>
+        <v>392</v>
       </c>
       <c r="C2" t="n">
-        <v>8027</v>
+        <v>2917</v>
       </c>
       <c r="D2" t="n">
-        <v>25422</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4242</v>
+        <v>1016</v>
       </c>
       <c r="C3" t="n">
-        <v>5518</v>
+        <v>4961</v>
       </c>
       <c r="D3" t="n">
-        <v>13069</v>
+        <v>13781</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2657</v>
+        <v>1208</v>
       </c>
       <c r="C4" t="n">
-        <v>6459</v>
+        <v>6421</v>
       </c>
       <c r="D4" t="n">
-        <v>7695</v>
+        <v>9112</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1986</v>
+        <v>594</v>
       </c>
       <c r="C5" t="n">
-        <v>6538</v>
+        <v>7332</v>
       </c>
       <c r="D5" t="n">
-        <v>3536</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1421</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>5538</v>
+        <v>4659</v>
       </c>
       <c r="D6" t="n">
-        <v>1503</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>834</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>3769</v>
+        <v>1456</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>396</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2110</v>
+        <v>516</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>979</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>426</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8891</v>
+        <v>518</v>
       </c>
       <c r="C2" t="n">
-        <v>5651</v>
+        <v>4290</v>
       </c>
       <c r="D2" t="n">
-        <v>20964</v>
+        <v>10965</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4865</v>
+        <v>634</v>
       </c>
       <c r="C3" t="n">
-        <v>8858</v>
+        <v>3474</v>
       </c>
       <c r="D3" t="n">
-        <v>14356</v>
+        <v>12561</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1835</v>
+        <v>989</v>
       </c>
       <c r="C4" t="n">
-        <v>9686</v>
+        <v>5592</v>
       </c>
       <c r="D4" t="n">
-        <v>7427</v>
+        <v>9641</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1313</v>
+        <v>768</v>
       </c>
       <c r="C5" t="n">
-        <v>5427</v>
+        <v>6803</v>
       </c>
       <c r="D5" t="n">
-        <v>2389</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>770</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>3693</v>
+        <v>5889</v>
       </c>
       <c r="D6" t="n">
-        <v>741</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>2067</v>
+        <v>2896</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>959</v>
+        <v>908</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5245</v>
+        <v>276</v>
       </c>
       <c r="C2" t="n">
-        <v>2779</v>
+        <v>2340</v>
       </c>
       <c r="D2" t="n">
-        <v>14810</v>
+        <v>8618</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5551</v>
+        <v>516</v>
       </c>
       <c r="C3" t="n">
-        <v>6767</v>
+        <v>3450</v>
       </c>
       <c r="D3" t="n">
-        <v>14565</v>
+        <v>11741</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2556</v>
+        <v>804</v>
       </c>
       <c r="C4" t="n">
-        <v>9482</v>
+        <v>4660</v>
       </c>
       <c r="D4" t="n">
-        <v>8341</v>
+        <v>9860</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1442</v>
+        <v>816</v>
       </c>
       <c r="C5" t="n">
-        <v>7250</v>
+        <v>6422</v>
       </c>
       <c r="D5" t="n">
-        <v>2942</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>900</v>
+        <v>434</v>
       </c>
       <c r="C6" t="n">
-        <v>4449</v>
+        <v>6513</v>
       </c>
       <c r="D6" t="n">
-        <v>896</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>2662</v>
+        <v>3944</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1261</v>
+        <v>1380</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4991</v>
+        <v>729</v>
       </c>
       <c r="C2" t="n">
-        <v>6872</v>
+        <v>5720</v>
       </c>
       <c r="D2" t="n">
-        <v>13755</v>
+        <v>11838</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4558</v>
+        <v>354</v>
       </c>
       <c r="C3" t="n">
-        <v>4424</v>
+        <v>2592</v>
       </c>
       <c r="D3" t="n">
-        <v>13619</v>
+        <v>10527</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3263</v>
+        <v>600</v>
       </c>
       <c r="C4" t="n">
-        <v>8007</v>
+        <v>3982</v>
       </c>
       <c r="D4" t="n">
-        <v>9103</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1685</v>
+        <v>750</v>
       </c>
       <c r="C5" t="n">
-        <v>8106</v>
+        <v>5538</v>
       </c>
       <c r="D5" t="n">
-        <v>3681</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1026</v>
+        <v>536</v>
       </c>
       <c r="C6" t="n">
-        <v>5660</v>
+        <v>6412</v>
       </c>
       <c r="D6" t="n">
-        <v>1178</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>486</v>
+        <v>210</v>
       </c>
       <c r="C7" t="n">
-        <v>3396</v>
+        <v>5063</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1822</v>
+        <v>2398</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>789</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3031</v>
+        <v>489</v>
       </c>
       <c r="C2" t="n">
-        <v>3318</v>
+        <v>3020</v>
       </c>
       <c r="D2" t="n">
-        <v>9595</v>
+        <v>8523</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4495</v>
+        <v>563</v>
       </c>
       <c r="C3" t="n">
-        <v>5087</v>
+        <v>3646</v>
       </c>
       <c r="D3" t="n">
-        <v>13328</v>
+        <v>11526</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3588</v>
+        <v>986</v>
       </c>
       <c r="C4" t="n">
-        <v>7508</v>
+        <v>5656</v>
       </c>
       <c r="D4" t="n">
-        <v>9688</v>
+        <v>10185</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>543</v>
       </c>
       <c r="C5" t="n">
-        <v>9396</v>
+        <v>8593</v>
       </c>
       <c r="D5" t="n">
-        <v>3887</v>
+        <v>4965</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>6601</v>
+        <v>6532</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>3446</v>
+        <v>2350</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1270</v>
+        <v>773</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3713</v>
+        <v>249</v>
       </c>
       <c r="C2" t="n">
-        <v>5267</v>
+        <v>2006</v>
       </c>
       <c r="D2" t="n">
-        <v>8641</v>
+        <v>6516</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3344</v>
+        <v>447</v>
       </c>
       <c r="C3" t="n">
-        <v>3840</v>
+        <v>2940</v>
       </c>
       <c r="D3" t="n">
-        <v>11975</v>
+        <v>10267</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3442</v>
+        <v>668</v>
       </c>
       <c r="C4" t="n">
-        <v>6308</v>
+        <v>4390</v>
       </c>
       <c r="D4" t="n">
-        <v>9952</v>
+        <v>9695</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2188</v>
+        <v>511</v>
       </c>
       <c r="C5" t="n">
-        <v>8384</v>
+        <v>6405</v>
       </c>
       <c r="D5" t="n">
-        <v>4604</v>
+        <v>5147</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>7824</v>
+        <v>6098</v>
       </c>
       <c r="D6" t="n">
-        <v>1524</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>4684</v>
+        <v>3010</v>
       </c>
       <c r="D7" t="n">
-        <v>621</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>2062</v>
+        <v>885</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>612</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2561</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
-        <v>3354</v>
+        <v>6684</v>
       </c>
       <c r="D2" t="n">
-        <v>6446</v>
+        <v>6691</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3032</v>
+        <v>295</v>
       </c>
       <c r="C3" t="n">
-        <v>3986</v>
+        <v>2132</v>
       </c>
       <c r="D3" t="n">
-        <v>10969</v>
+        <v>8927</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3142</v>
+        <v>495</v>
       </c>
       <c r="C4" t="n">
-        <v>5387</v>
+        <v>3491</v>
       </c>
       <c r="D4" t="n">
-        <v>9997</v>
+        <v>9510</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2394</v>
+        <v>529</v>
       </c>
       <c r="C5" t="n">
-        <v>7733</v>
+        <v>5250</v>
       </c>
       <c r="D5" t="n">
-        <v>5117</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1273</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>8322</v>
+        <v>6187</v>
       </c>
       <c r="D6" t="n">
-        <v>1772</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>5741</v>
+        <v>4581</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2664</v>
+        <v>1892</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>550</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3320</v>
+        <v>459</v>
       </c>
       <c r="C2" t="n">
-        <v>11400</v>
+        <v>8658</v>
       </c>
       <c r="D2" t="n">
-        <v>12653</v>
+        <v>12770</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2416</v>
+        <v>189</v>
       </c>
       <c r="C3" t="n">
-        <v>3334</v>
+        <v>3828</v>
       </c>
       <c r="D3" t="n">
-        <v>9829</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2697</v>
+        <v>350</v>
       </c>
       <c r="C4" t="n">
-        <v>4696</v>
+        <v>2713</v>
       </c>
       <c r="D4" t="n">
-        <v>9727</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2431</v>
+        <v>469</v>
       </c>
       <c r="C5" t="n">
-        <v>6648</v>
+        <v>4262</v>
       </c>
       <c r="D5" t="n">
-        <v>5617</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1522</v>
+        <v>373</v>
       </c>
       <c r="C6" t="n">
-        <v>8033</v>
+        <v>5672</v>
       </c>
       <c r="D6" t="n">
-        <v>2166</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>517</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>6674</v>
+        <v>5334</v>
       </c>
       <c r="D7" t="n">
-        <v>808</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>3744</v>
+        <v>3103</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1317</v>
+        <v>1128</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7797</v>
+        <v>2788</v>
       </c>
       <c r="C2" t="n">
-        <v>11101</v>
+        <v>14091</v>
       </c>
       <c r="D2" t="n">
-        <v>9623</v>
+        <v>14524</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2402</v>
+        <v>482</v>
       </c>
       <c r="C2" t="n">
-        <v>6657</v>
+        <v>6622</v>
       </c>
       <c r="D2" t="n">
-        <v>9413</v>
+        <v>13163</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>245</v>
       </c>
       <c r="C3" t="n">
-        <v>5374</v>
+        <v>5268</v>
       </c>
       <c r="D3" t="n">
-        <v>10798</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3603</v>
+        <v>247</v>
       </c>
       <c r="C4" t="n">
-        <v>6966</v>
+        <v>3181</v>
       </c>
       <c r="D4" t="n">
-        <v>10032</v>
+        <v>8584</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1451</v>
+        <v>384</v>
       </c>
       <c r="C5" t="n">
-        <v>10588</v>
+        <v>3433</v>
       </c>
       <c r="D5" t="n">
-        <v>5126</v>
+        <v>6511</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>477</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>8036</v>
+        <v>4994</v>
       </c>
       <c r="D6" t="n">
-        <v>1729</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="C7" t="n">
-        <v>3669</v>
+        <v>5477</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1290</v>
+        <v>3989</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>348</v>
+        <v>1921</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>639</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8181</v>
+        <v>3217</v>
       </c>
       <c r="C2" t="n">
-        <v>6299</v>
+        <v>9773</v>
       </c>
       <c r="D2" t="n">
-        <v>8871</v>
+        <v>20962</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3311</v>
+        <v>902</v>
       </c>
       <c r="C3" t="n">
-        <v>5594</v>
+        <v>5564</v>
       </c>
       <c r="D3" t="n">
-        <v>2255</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5239</v>
+        <v>1595</v>
       </c>
       <c r="C2" t="n">
-        <v>7190</v>
+        <v>4067</v>
       </c>
       <c r="D2" t="n">
-        <v>18074</v>
+        <v>27554</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4720</v>
+        <v>1743</v>
       </c>
       <c r="C3" t="n">
-        <v>5168</v>
+        <v>6951</v>
       </c>
       <c r="D3" t="n">
-        <v>3200</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1473</v>
+        <v>444</v>
       </c>
       <c r="C4" t="n">
-        <v>3321</v>
+        <v>3520</v>
       </c>
       <c r="D4" t="n">
-        <v>1635</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4570</v>
+        <v>1470</v>
       </c>
       <c r="C2" t="n">
-        <v>10801</v>
+        <v>7314</v>
       </c>
       <c r="D2" t="n">
-        <v>30847</v>
+        <v>25335</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4104</v>
+        <v>1391</v>
       </c>
       <c r="C3" t="n">
-        <v>5419</v>
+        <v>4552</v>
       </c>
       <c r="D3" t="n">
-        <v>5349</v>
+        <v>8898</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2635</v>
+        <v>946</v>
       </c>
       <c r="C4" t="n">
-        <v>4248</v>
+        <v>5488</v>
       </c>
       <c r="D4" t="n">
-        <v>1885</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>652</v>
+        <v>237</v>
       </c>
       <c r="C5" t="n">
-        <v>1912</v>
+        <v>2111</v>
       </c>
       <c r="D5" t="n">
-        <v>1229</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5701</v>
+        <v>2386</v>
       </c>
       <c r="C2" t="n">
-        <v>13727</v>
+        <v>4694</v>
       </c>
       <c r="D2" t="n">
-        <v>31016</v>
+        <v>30337</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3569</v>
+        <v>1180</v>
       </c>
       <c r="C3" t="n">
-        <v>7093</v>
+        <v>5243</v>
       </c>
       <c r="D3" t="n">
-        <v>8848</v>
+        <v>10887</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2865</v>
+        <v>1007</v>
       </c>
       <c r="C4" t="n">
-        <v>4777</v>
+        <v>4843</v>
       </c>
       <c r="D4" t="n">
-        <v>2459</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1331</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
-        <v>3042</v>
+        <v>3914</v>
       </c>
       <c r="D5" t="n">
-        <v>1293</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>338</v>
+        <v>158</v>
       </c>
       <c r="C6" t="n">
-        <v>1103</v>
+        <v>1235</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6861</v>
+        <v>1898</v>
       </c>
       <c r="C2" t="n">
-        <v>11261</v>
+        <v>7321</v>
       </c>
       <c r="D2" t="n">
-        <v>23640</v>
+        <v>28004</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3325</v>
+        <v>1420</v>
       </c>
       <c r="C3" t="n">
-        <v>8539</v>
+        <v>4330</v>
       </c>
       <c r="D3" t="n">
-        <v>10907</v>
+        <v>13076</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1978</v>
+        <v>934</v>
       </c>
       <c r="C4" t="n">
-        <v>4934</v>
+        <v>4906</v>
       </c>
       <c r="D4" t="n">
-        <v>3099</v>
+        <v>4797</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1094</v>
+        <v>647</v>
       </c>
       <c r="C5" t="n">
-        <v>2841</v>
+        <v>4314</v>
       </c>
       <c r="D5" t="n">
-        <v>1178</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>385</v>
+        <v>283</v>
       </c>
       <c r="C6" t="n">
-        <v>1388</v>
+        <v>2559</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>454</v>
+        <v>755</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5409</v>
+        <v>2249</v>
       </c>
       <c r="C2" t="n">
-        <v>7154</v>
+        <v>10365</v>
       </c>
       <c r="D2" t="n">
-        <v>17222</v>
+        <v>23607</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4242</v>
+        <v>1342</v>
       </c>
       <c r="C3" t="n">
-        <v>8700</v>
+        <v>5040</v>
       </c>
       <c r="D3" t="n">
-        <v>12243</v>
+        <v>14326</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2287</v>
+        <v>981</v>
       </c>
       <c r="C4" t="n">
-        <v>6977</v>
+        <v>4516</v>
       </c>
       <c r="D4" t="n">
-        <v>4578</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>3987</v>
+        <v>4467</v>
       </c>
       <c r="D5" t="n">
-        <v>1499</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>673</v>
+        <v>398</v>
       </c>
       <c r="C6" t="n">
-        <v>2180</v>
+        <v>3358</v>
       </c>
       <c r="D6" t="n">
-        <v>827</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>966</v>
+        <v>1585</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>342</v>
+        <v>501</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4263</v>
+        <v>2027</v>
       </c>
       <c r="C2" t="n">
-        <v>9740</v>
+        <v>6467</v>
       </c>
       <c r="D2" t="n">
-        <v>14557</v>
+        <v>18782</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3949</v>
+        <v>1750</v>
       </c>
       <c r="C3" t="n">
-        <v>6853</v>
+        <v>8223</v>
       </c>
       <c r="D3" t="n">
-        <v>12137</v>
+        <v>15548</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2750</v>
+        <v>639</v>
       </c>
       <c r="C4" t="n">
-        <v>7774</v>
+        <v>7062</v>
       </c>
       <c r="D4" t="n">
-        <v>5792</v>
+        <v>5562</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1604</v>
+        <v>367</v>
       </c>
       <c r="C5" t="n">
-        <v>5444</v>
+        <v>3290</v>
       </c>
       <c r="D5" t="n">
-        <v>2015</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>158</v>
       </c>
       <c r="C6" t="n">
-        <v>3092</v>
+        <v>1553</v>
       </c>
       <c r="D6" t="n">
-        <v>923</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>1584</v>
+        <v>490</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>647</v>
+        <v>275</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
